--- a/questionnaire_templates/025_stool_consistency_assessment_questionnaire--questionnaire_templates.xlsx
+++ b/questionnaire_templates/025_stool_consistency_assessment_questionnaire--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,12 +1079,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_loose'}</t>
+          <t>very_loose</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very loose'}</t>
+          <t>Very loose</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'loose'}</t>
+          <t>loose</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Loose'}</t>
+          <t>Loose</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'loose'}</t>
+          <t>very_firm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Loose'}</t>
+          <t>Very firm</t>
         </is>
       </c>
     </row>
@@ -1180,29 +1180,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_firm'}</t>
+          <t>firm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very firm'}</t>
+          <t>Firm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bowel_habits_choices</t>
+          <t>stool_consistency_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'firm'}</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Firm'}</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'type_1'}</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Type 1'}</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'type_2'}</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Type 2'}</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
@@ -1248,29 +1248,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'type_3'}</t>
+          <t>type_4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Type 3'}</t>
+          <t>Type 4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stool_consistency_choices</t>
+          <t>follow_up_questions_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'type_4'}</t>
+          <t>how_often_do_you_have_bowel_movements?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Type 4'}</t>
+          <t>How often do you have bowel movements?</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'how_often_do_you_have_bowel_movements?'}</t>
+          <t>how_long_do_you_spend_in_the_bathroom?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'How often do you have bowel movements?'}</t>
+          <t>How long do you spend in the bathroom?</t>
         </is>
       </c>
     </row>
@@ -1299,29 +1299,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'how_long_do_you_spend_in_the_bathroom?'}</t>
+          <t>are_you_satisfied_with_your_bowel_movements?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'How long do you spend in the bathroom?'}</t>
+          <t>Are you satisfied with your bowel movements?</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>follow_up_questions_choices</t>
+          <t>research_questions_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'are_you_satisfied_with_your_bowel_movements?'}</t>
+          <t>how_often_do_you_experience_abdominal_pain?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Are you satisfied with your bowel movements?'}</t>
+          <t>How often do you experience abdominal pain?</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'how_often_do_you_experience_abdominal_pain?'}</t>
+          <t>how_often_do_you_experience_bloating?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'How often do you experience abdominal pain?'}</t>
+          <t>How often do you experience bloating?</t>
         </is>
       </c>
     </row>
@@ -1350,29 +1350,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'how_often_do_you_experience_bloating?'}</t>
+          <t>how_often_do_you_experience_bowel_irregularity?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'How often do you experience bloating?'}</t>
+          <t>How often do you experience bowel irregularity?</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>research_questions_choices</t>
+          <t>intake_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'how_often_do_you_experience_bowel_irregularity?'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'How often do you experience bowel irregularity?'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>every_other_day</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Every other day</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'every_other_day'}</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Every other day'}</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
@@ -1418,29 +1418,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'3-4_times_a_week'}</t>
+          <t>less_than_3_times_a_week</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': '3-4 times a week'}</t>
+          <t>Less than 3 times a week</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intake_frequency_choices</t>
+          <t>follow_up_frequency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_3_times_a_week'}</t>
+          <t>1-2_months</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 3 times a week'}</t>
+          <t>1-2 months</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_months'}</t>
+          <t>every_3-6_months</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': '1-2 months'}</t>
+          <t>Every 3-6 months</t>
         </is>
       </c>
     </row>
@@ -1469,29 +1469,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'every_3-6_months'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Every 3-6 months'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>follow_up_frequency_choices</t>
+          <t>research_frequency_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>every_other_day</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Every other day</t>
         </is>
       </c>
     </row>
@@ -1520,29 +1520,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'every_other_day'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Every other day'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>research_frequency_choices</t>
+          <t>bowel_movement_frequency_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>every_other_day</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Every other day</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'every_other_day'}</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Every other day'}</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
@@ -1588,29 +1588,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'3-4_times_a_week'}</t>
+          <t>less_than_3_times_a_week</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': '3-4 times a week'}</t>
+          <t>Less than 3 times a week</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bowel_movement_frequency_choices</t>
+          <t>symptoms_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_3_times_a_week'}</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 3 times a week'}</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'diarrhea'}</t>
+          <t>abdominal_pain</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Diarrhea'}</t>
+          <t>Abdominal pain</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'abdominal_pain'}</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Abdominal pain'}</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'nausea'}</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Nausea'}</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
@@ -1673,29 +1673,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'vomiting'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Vomiting'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>additional_symptoms_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>abdominal_pain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Abdominal pain</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'abdominal_pain'}</t>
+          <t>bloating</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Abdominal pain'}</t>
+          <t>Bloating</t>
         </is>
       </c>
     </row>
@@ -1724,12 +1724,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'bloating'}</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Bloating'}</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'diarrhea'}</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Diarrhea'}</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -1758,29 +1758,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'nausea'}</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Nausea'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>additional_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'label':_'vomiting'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'label': 'Vomiting'}</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
